--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,126 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Avinash</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dadhboard</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Running</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Renovora Tech</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kiran</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Santgram</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Renovora Tech</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kiran</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Renora Ai</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Running</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Renovora Tech</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sarthak</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Khel Re</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Renovora Tech</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kiran</t>
         </is>
       </c>
     </row>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,172 +441,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>client</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>deadline</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>client</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>santparampra.in</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Running</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Sant Parampra</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Avinash</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Dadhboard</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Running</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Renovora Tech</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Kiran</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Santgram</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Testing</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Renovora Tech</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Kiran</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Renora Ai</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Running</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Renovora Tech</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Sarthak</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Khel Re</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Testing</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Renovora Tech</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Kiran</t>
         </is>
       </c>
     </row>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,52 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>deadline</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>costing</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>santparampra.in</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sant Parampra</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Avinash Ganesh Chate</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Running</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
